--- a/data/ct_scoop/ct_scoop_links_2026-06-29.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-06-29.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,52 +440,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MERIDEN SCOOP: New barber academy coming to Meriden Mall</t>
+          <t>NEWINGTON &amp; SOUTH WINDSOR SCOOP: Colony Grill eyeing possible new locations!</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-new-barber-academy-coming-to-meriden-mall</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-south-windsor-scoop-colony-grill-eyeing-possible-new-locations</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WEST HARTFORD SCOOP: New businesses &amp; restaurants coming to West Hartford Center</t>
+          <t>EAST WINDSOR SCOOP: Molly's Sweet Spot celebrates opening in East Windsor</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-new-businesses-restaurants-coming-to-west-hartford-center</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/east-windsor-scoop-mollys-sweet-spot-celebrates-opening-in-east-windsor</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLAINVILLE SCOOP: Dairy Queen to reopen under new ownership</t>
+          <t>MERIDEN SCOOP: New barber academy coming to Meriden Mall</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/plainville-scoop-dairy-queen-to-reopen-under-new-ownership</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-new-barber-academy-coming-to-meriden-mall</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WETHERSFIELD REVIEW: River - A Waterfront Restaurant &amp; Bar</t>
+          <t>WEST HARTFORD SCOOP: New businesses &amp; restaurants coming to West Hartford Center</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -493,14 +493,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/wethersfield-review-river-a-waterfront-restaurant-bar</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-new-businesses-restaurants-coming-to-west-hartford-center</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOUTH WINDSOR SCOOP: Pandora opens at The Shops at Evergreen Walk!</t>
+          <t>PLAINVILLE SCOOP: Dairy Queen to reopen under new ownership</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -508,14 +508,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-pandora-opens-at-the-shops-at-evergreen-walk</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/plainville-scoop-dairy-queen-to-reopen-under-new-ownership</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WATERFORD SCOOP: New retailers start construction in Waterford</t>
+          <t>WETHERSFIELD REVIEW: River - A Waterfront Restaurant &amp; Bar</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -523,14 +523,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/waterford-scoop-new-retailers-start-construction-in-waterford</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/wethersfield-review-river-a-waterfront-restaurant-bar</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OLD SAYBROOK SCOOP: New plaza at Max's Place approved, Chipotle &amp; Jersey Mike's eyed along with others!</t>
+          <t>SOUTH WINDSOR SCOOP: Pandora opens at The Shops at Evergreen Walk!</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -538,20 +538,50 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-middlesex-county-posts/old-saybrook-scoop-new-plaza-at-maxs-place-approved-chipotle-jersey-mikes-eyed-along-with-others</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-pandora-opens-at-the-shops-at-evergreen-walk</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>WATERFORD SCOOP: New retailers start construction in Waterford</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/waterford-scoop-new-retailers-start-construction-in-waterford</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OLD SAYBROOK SCOOP: New plaza at Max's Place approved, Chipotle &amp; Jersey Mike's eyed along with others!</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-middlesex-county-posts/old-saybrook-scoop-new-plaza-at-maxs-place-approved-chipotle-jersey-mikes-eyed-along-with-others</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>WEST SPRINGFIELD SCOOP: Work begins on Massachusetts first Ross Dress for Less!</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B11" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-mass-posts/west-springfield-scoop-work-begins-on-massachusetts-first-ross-dress-for-less</t>
         </is>
